--- a/upload/Data_Riska_Ujang_TFL_IBUN.xlsx
+++ b/upload/Data_Riska_Ujang_TFL_IBUN.xlsx
@@ -400,20 +400,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L51"/>
-  <cols>
-    <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="25.83203125" customWidth="1"/>
-    <col min="3" max="3" width="5.83203125" customWidth="1"/>
-    <col min="4" max="4" width="20.83203125" customWidth="1"/>
-    <col min="5" max="5" width="20.83203125" customWidth="1"/>
-    <col min="6" max="6" width="35.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="18.83203125" customWidth="1"/>
-    <col min="9" max="9" width="18.83203125" customWidth="1"/>
-    <col min="10" max="10" width="15.83203125" customWidth="1"/>
-    <col min="11" max="11" width="30.83203125" customWidth="1"/>
-    <col min="12" max="12" width="25.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1037,19 +1023,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>WAWAN SETIAWAN</v>
+        <v>Encar</v>
       </c>
       <c r="C17" t="str">
         <v>L</v>
       </c>
       <c r="D17" t="str">
-        <v>3204360204940003</v>
+        <v>3204364101600008</v>
       </c>
       <c r="E17" t="str">
-        <v>3204360404180010</v>
+        <v>3204360612130038</v>
       </c>
       <c r="F17" t="str">
-        <v>KP. AWILEGA. RT 3 RW 9</v>
+        <v>KP. Citeureup 002/008</v>
       </c>
       <c r="G17" t="str">
         <v>LAMPEGAN</v>
@@ -1075,19 +1061,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>ARIEF MOCHAMAD IKBAL</v>
+        <v>Andri</v>
       </c>
       <c r="C18" t="str">
         <v>L</v>
       </c>
       <c r="D18" t="str">
-        <v>3204360103920008</v>
+        <v>3204360907970002</v>
       </c>
       <c r="E18" t="str">
-        <v>3204361302180005</v>
+        <v>3204361809190001</v>
       </c>
       <c r="F18" t="str">
-        <v>KP. BABAKAN SALAM RT 2 RW 7</v>
+        <v>KP. Cikonyal 001/011</v>
       </c>
       <c r="G18" t="str">
         <v>LAMPEGAN</v>
@@ -1113,19 +1099,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>ASIH</v>
+        <v>Dedeh</v>
       </c>
       <c r="C19" t="str">
         <v>P</v>
       </c>
       <c r="D19" t="str">
-        <v>3204364907640002</v>
+        <v>3204364107680030</v>
       </c>
       <c r="E19" t="str">
-        <v>3204362406140007</v>
+        <v>3204360112120006</v>
       </c>
       <c r="F19" t="str">
-        <v>KP. BABAKAN SALAM. RT 1 RW 7</v>
+        <v>KP. Citeureup 002/008</v>
       </c>
       <c r="G19" t="str">
         <v>LAMPEGAN</v>
@@ -1151,19 +1137,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>YATI</v>
+        <v>Memen</v>
       </c>
       <c r="C20" t="str">
         <v>P</v>
       </c>
       <c r="D20" t="str">
-        <v>3204364802550002</v>
+        <v>3204351103720001</v>
       </c>
       <c r="E20" t="str">
-        <v>3204363108120020</v>
+        <v>3204363112190003</v>
       </c>
       <c r="F20" t="str">
-        <v>KP. JOLOK RT 2 RW 6</v>
+        <v>KP. Jolok 001/006</v>
       </c>
       <c r="G20" t="str">
         <v>LAMPEGAN</v>
@@ -1189,19 +1175,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>ROHMAT</v>
+        <v>Sodikin</v>
       </c>
       <c r="C21" t="str">
         <v>L</v>
       </c>
       <c r="D21" t="str">
-        <v>3204363001760001</v>
+        <v>3204330703920003</v>
       </c>
       <c r="E21" t="str">
-        <v>3204361809080057</v>
+        <v>3204361706200001</v>
       </c>
       <c r="F21" t="str">
-        <v>KP. JOLOK RT 1 RW 6</v>
+        <v>KP. Jolok 001/006</v>
       </c>
       <c r="G21" t="str">
         <v>LAMPEGAN</v>
@@ -1379,19 +1365,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>Ai Maryati</v>
+        <v>Cecep</v>
       </c>
       <c r="C26" t="str">
         <v>P</v>
       </c>
       <c r="D26" t="str">
-        <v>3204365206620003</v>
+        <v>3204360102550003</v>
       </c>
       <c r="E26" t="str">
-        <v>3204361903051928</v>
+        <v>3204361903051912</v>
       </c>
       <c r="F26" t="str">
-        <v>Babakan Salam</v>
+        <v>JL. Pangguh 001/007</v>
       </c>
       <c r="G26" t="str">
         <v>LAMPEGAN</v>
@@ -2372,10 +2358,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B11"/>
-  <cols>
-    <col min="1" max="1" width="25.83203125" customWidth="1"/>
-    <col min="2" max="2" width="40.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">

--- a/upload/Data_Riska_Ujang_TFL_IBUN.xlsx
+++ b/upload/Data_Riska_Ujang_TFL_IBUN.xlsx
@@ -1023,7 +1023,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>Encar</v>
+        <v>Wawan Setiawan</v>
       </c>
       <c r="C17" t="str">
         <v>L</v>
@@ -1050,7 +1050,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K17" t="str">
-        <v>Backlog 2 desil 6</v>
+        <v>Backlog 2 desil 6 | Data Pengganti</v>
       </c>
       <c r="L17" t="str">
         <v>Backlog 2 Desil 6-10</v>
@@ -1061,7 +1061,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>Andri</v>
+        <v>Arief Mochamad Ikbal</v>
       </c>
       <c r="C18" t="str">
         <v>L</v>
@@ -1088,7 +1088,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K18" t="str">
-        <v>Backlog 2 desil 1</v>
+        <v>Backlog 2 desil 1 | Data Pengganti</v>
       </c>
       <c r="L18" t="str">
         <v>Backlog 2 Desil 1-5</v>
@@ -1099,7 +1099,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>Dedeh</v>
+        <v>Asih</v>
       </c>
       <c r="C19" t="str">
         <v>P</v>
@@ -1126,7 +1126,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K19" t="str">
-        <v>Backlog 2 desil 2</v>
+        <v>Backlog 2 desil 2 | Data Pengganti</v>
       </c>
       <c r="L19" t="str">
         <v>Backlog 2 Desil 1-5</v>
@@ -1137,7 +1137,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>Memen</v>
+        <v>Yati</v>
       </c>
       <c r="C20" t="str">
         <v>P</v>
@@ -1164,7 +1164,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K20" t="str">
-        <v>Backlog 2 desil 2</v>
+        <v>Backlog 2 desil 2 | Data Pengganti</v>
       </c>
       <c r="L20" t="str">
         <v>Backlog 2 Desil 1-5</v>
@@ -1175,7 +1175,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>Sodikin</v>
+        <v>Rohmat</v>
       </c>
       <c r="C21" t="str">
         <v>L</v>
@@ -1202,7 +1202,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K21" t="str">
-        <v>Backlog 2 desil 2</v>
+        <v>Backlog 2 desil 2 | Data Pengganti</v>
       </c>
       <c r="L21" t="str">
         <v>Backlog 2 Desil 1-5</v>
@@ -1365,7 +1365,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>Cecep</v>
+        <v>Ai Maryati</v>
       </c>
       <c r="C26" t="str">
         <v>P</v>
@@ -1392,7 +1392,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K26" t="str">
-        <v>Backlog 2 desil 2</v>
+        <v>Backlog 2 desil 2 | Data Pengganti</v>
       </c>
       <c r="L26" t="str">
         <v>Backlog 2 Desil 1-5</v>

--- a/upload/Data_Riska_Ujang_TFL_IBUN.xlsx
+++ b/upload/Data_Riska_Ujang_TFL_IBUN.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L57"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2348,9 +2348,237 @@
         <v>Backlog 2 Desil 1-5</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="str">
+        <v>NURHAYATI</v>
+      </c>
+      <c r="C52" t="str">
+        <v>P</v>
+      </c>
+      <c r="D52" t="str">
+        <v>3204354805770008</v>
+      </c>
+      <c r="E52" t="str">
+        <v>3204351903050323</v>
+      </c>
+      <c r="F52" t="str">
+        <v>KP CILOPANG RT 02 RW 07</v>
+      </c>
+      <c r="G52" t="str">
+        <v>LOA</v>
+      </c>
+      <c r="H52" t="str">
+        <v>PASEH</v>
+      </c>
+      <c r="I52" t="str">
+        <v>KAB. BANDUNG</v>
+      </c>
+      <c r="J52" t="str">
+        <v>JAWA BARAT</v>
+      </c>
+      <c r="K52" t="str">
+        <v>Data Pengganti</v>
+      </c>
+      <c r="L52" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="str">
+        <v>ECIN</v>
+      </c>
+      <c r="C53" t="str">
+        <v>P</v>
+      </c>
+      <c r="D53" t="str">
+        <v>3204356010480002</v>
+      </c>
+      <c r="E53" t="str">
+        <v>3204352312050057</v>
+      </c>
+      <c r="F53" t="str">
+        <v>KP BARUNAI RT 00/04</v>
+      </c>
+      <c r="G53" t="str">
+        <v>LOA</v>
+      </c>
+      <c r="H53" t="str">
+        <v>PASEH</v>
+      </c>
+      <c r="I53" t="str">
+        <v>KAB. BANDUNG</v>
+      </c>
+      <c r="J53" t="str">
+        <v>JAWA BARAT</v>
+      </c>
+      <c r="K53" t="str">
+        <v>Data Pengganti</v>
+      </c>
+      <c r="L53" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="str">
+        <v>ASEP AAN SAEPUDIN</v>
+      </c>
+      <c r="C54" t="str">
+        <v>L</v>
+      </c>
+      <c r="D54" t="str">
+        <v>3204350901750002</v>
+      </c>
+      <c r="E54" t="str">
+        <v>3204351208160008</v>
+      </c>
+      <c r="F54" t="str">
+        <v>KP LOA RT 01/01</v>
+      </c>
+      <c r="G54" t="str">
+        <v>LOA</v>
+      </c>
+      <c r="H54" t="str">
+        <v>PASEH</v>
+      </c>
+      <c r="I54" t="str">
+        <v>KAB. BANDUNG</v>
+      </c>
+      <c r="J54" t="str">
+        <v>JAWA BARAT</v>
+      </c>
+      <c r="K54" t="str">
+        <v>Data Pengganti</v>
+      </c>
+      <c r="L54" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="str">
+        <v>DANA</v>
+      </c>
+      <c r="C55" t="str">
+        <v>L</v>
+      </c>
+      <c r="D55" t="str">
+        <v>3204352610750003</v>
+      </c>
+      <c r="E55" t="str">
+        <v>3204351903051537</v>
+      </c>
+      <c r="F55" t="str">
+        <v>KP SUKA GEUNAH RT 01/05</v>
+      </c>
+      <c r="G55" t="str">
+        <v>LOA</v>
+      </c>
+      <c r="H55" t="str">
+        <v>PASEH</v>
+      </c>
+      <c r="I55" t="str">
+        <v>KAB. BANDUNG</v>
+      </c>
+      <c r="J55" t="str">
+        <v>JAWA BARAT</v>
+      </c>
+      <c r="K55" t="str">
+        <v>Data Pengganti</v>
+      </c>
+      <c r="L55" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="str">
+        <v>TARLAN</v>
+      </c>
+      <c r="C56" t="str">
+        <v>L</v>
+      </c>
+      <c r="D56" t="str">
+        <v>3204351808630003</v>
+      </c>
+      <c r="E56" t="str">
+        <v>3204352405110065</v>
+      </c>
+      <c r="F56" t="str">
+        <v>KP CILOPANG RT 04/07</v>
+      </c>
+      <c r="G56" t="str">
+        <v>LOA</v>
+      </c>
+      <c r="H56" t="str">
+        <v>PASEH</v>
+      </c>
+      <c r="I56" t="str">
+        <v>KAB. BANDUNG</v>
+      </c>
+      <c r="J56" t="str">
+        <v>JAWA BARAT</v>
+      </c>
+      <c r="K56" t="str">
+        <v>Data Pengganti</v>
+      </c>
+      <c r="L56" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="str">
+        <v>AHMAD</v>
+      </c>
+      <c r="C57" t="str">
+        <v>L</v>
+      </c>
+      <c r="D57" t="str">
+        <v>3204351702540001</v>
+      </c>
+      <c r="E57" t="str">
+        <v>3204352508050248</v>
+      </c>
+      <c r="F57" t="str">
+        <v>KP. CILOPANG 001/003</v>
+      </c>
+      <c r="G57" t="str">
+        <v>LOA</v>
+      </c>
+      <c r="H57" t="str">
+        <v>PASEH</v>
+      </c>
+      <c r="I57" t="str">
+        <v>KAB. BANDUNG</v>
+      </c>
+      <c r="J57" t="str">
+        <v>JAWA BARAT</v>
+      </c>
+      <c r="K57" t="str">
+        <v>Data Pengganti</v>
+      </c>
+      <c r="L57" t="str">
+        <v>-</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L57"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2404,7 +2632,7 @@
         <v>Total Penerima</v>
       </c>
       <c r="B6" t="str">
-        <v>50</v>
+        <v>56 orang</v>
       </c>
     </row>
     <row r="7">
@@ -2428,7 +2656,7 @@
         <v>LOA (PASEH)</v>
       </c>
       <c r="B9" t="str">
-        <v>20 orang</v>
+        <v>20 + 6 pengganti orang</v>
       </c>
     </row>
     <row r="10">
@@ -2436,7 +2664,7 @@
         <v>Laki-laki</v>
       </c>
       <c r="B10" t="str">
-        <v>39 orang</v>
+        <v>43 orang</v>
       </c>
     </row>
     <row r="11">
@@ -2444,7 +2672,7 @@
         <v>Perempuan</v>
       </c>
       <c r="B11" t="str">
-        <v>11 orang</v>
+        <v>13 orang</v>
       </c>
     </row>
   </sheetData>

--- a/upload/Data_Riska_Ujang_TFL_IBUN.xlsx
+++ b/upload/Data_Riska_Ujang_TFL_IBUN.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L57"/>
+  <dimension ref="A1:L50"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1593,19 +1593,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="str">
-        <v>ADANG</v>
+        <v>AAM</v>
       </c>
       <c r="C32" t="str">
-        <v>P</v>
+        <v>L</v>
       </c>
       <c r="D32" t="str">
-        <v>3204364406880002</v>
+        <v>3204350610650002</v>
       </c>
       <c r="E32" t="str">
-        <v>3204361108120039</v>
+        <v>3204352312050145</v>
       </c>
       <c r="F32" t="str">
-        <v>KP. CICANAR RT 1 RW 12</v>
+        <v>KP LENGGO RT 2 RW 11</v>
       </c>
       <c r="G32" t="str">
         <v>LOA</v>
@@ -1620,10 +1620,10 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K32" t="str">
-        <v>Backlog 2 desil 2</v>
+        <v>-</v>
       </c>
       <c r="L32" t="str">
-        <v>Backlog 2 Desil 1-5</v>
+        <v>-</v>
       </c>
     </row>
     <row r="33">
@@ -1631,19 +1631,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="str">
-        <v>EHA</v>
+        <v>ENGKUS</v>
       </c>
       <c r="C33" t="str">
-        <v>P</v>
+        <v>L</v>
       </c>
       <c r="D33" t="str">
-        <v>3204355002550004</v>
+        <v>3204350408910001</v>
       </c>
       <c r="E33" t="str">
-        <v>3204353009220015</v>
+        <v>3204350807190015</v>
       </c>
       <c r="F33" t="str">
-        <v>KP. LOA RT 3 RW 10</v>
+        <v>KP TIISDINGIN RT 2 RW 6</v>
       </c>
       <c r="G33" t="str">
         <v>LOA</v>
@@ -1658,10 +1658,10 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K33" t="str">
-        <v>Backlog 2 desil 1</v>
+        <v>-</v>
       </c>
       <c r="L33" t="str">
-        <v>Backlog 2 Desil 1-5</v>
+        <v>-</v>
       </c>
     </row>
     <row r="34">
@@ -1669,19 +1669,19 @@
         <v>33</v>
       </c>
       <c r="B34" t="str">
-        <v>LALAN</v>
+        <v>ENDANG</v>
       </c>
       <c r="C34" t="str">
         <v>L</v>
       </c>
       <c r="D34" t="str">
-        <v>3204352905980001</v>
+        <v>3204352504720003</v>
       </c>
       <c r="E34" t="str">
-        <v>3204351612210006</v>
+        <v>3204352508050102</v>
       </c>
       <c r="F34" t="str">
-        <v>KP. CIDADAP RT 5 RW 5</v>
+        <v>KP LOA RT 3 RW 10</v>
       </c>
       <c r="G34" t="str">
         <v>LOA</v>
@@ -1696,10 +1696,10 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K34" t="str">
-        <v>Backlog 2 desil 2</v>
+        <v>-</v>
       </c>
       <c r="L34" t="str">
-        <v>Backlog 2 Desil 1-5</v>
+        <v>-</v>
       </c>
     </row>
     <row r="35">
@@ -1707,19 +1707,19 @@
         <v>34</v>
       </c>
       <c r="B35" t="str">
-        <v>ENGKUS</v>
+        <v>SARIFUDIN</v>
       </c>
       <c r="C35" t="str">
         <v>L</v>
       </c>
       <c r="D35" t="str">
-        <v>3204350408910001</v>
+        <v>3204352307940008</v>
       </c>
       <c r="E35" t="str">
-        <v>3204350807190015</v>
+        <v>3204352609140021</v>
       </c>
       <c r="F35" t="str">
-        <v>KP. TIISDINGIN RT 2 RW 6</v>
+        <v>KP LOA RT 3 RW 10</v>
       </c>
       <c r="G35" t="str">
         <v>LOA</v>
@@ -1734,10 +1734,10 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K35" t="str">
-        <v>Tidak masuk backlog perumahan desil 1</v>
+        <v>-</v>
       </c>
       <c r="L35" t="str">
-        <v>Tidak masuk backlog perumahan</v>
+        <v>-</v>
       </c>
     </row>
     <row r="36">
@@ -1745,19 +1745,19 @@
         <v>35</v>
       </c>
       <c r="B36" t="str">
-        <v>ENDANG</v>
+        <v>AHMAD</v>
       </c>
       <c r="C36" t="str">
         <v>L</v>
       </c>
       <c r="D36" t="str">
-        <v>3204352504720003</v>
+        <v>3204351702540001</v>
       </c>
       <c r="E36" t="str">
-        <v>3204352508050102</v>
+        <v>3204352508050248</v>
       </c>
       <c r="F36" t="str">
-        <v>KP LOA RT 3 RW 10</v>
+        <v>KP CILOPANG 001/003</v>
       </c>
       <c r="G36" t="str">
         <v>LOA</v>
@@ -1772,10 +1772,10 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K36" t="str">
-        <v>Backlog 2 desil 3</v>
+        <v>Data Baru</v>
       </c>
       <c r="L36" t="str">
-        <v>Backlog 2 Desil 1-5</v>
+        <v>-</v>
       </c>
     </row>
     <row r="37">
@@ -1783,19 +1783,19 @@
         <v>36</v>
       </c>
       <c r="B37" t="str">
-        <v>WARSA</v>
+        <v>ASEP AAN SAEPUDIN</v>
       </c>
       <c r="C37" t="str">
         <v>L</v>
       </c>
       <c r="D37" t="str">
-        <v>3204351002711001</v>
+        <v>3204350901750002</v>
       </c>
       <c r="E37" t="str">
-        <v>3204351609140013</v>
+        <v>3204351208160008</v>
       </c>
       <c r="F37" t="str">
-        <v>KP. BUKATANAH. RT 2 RW 3</v>
+        <v>KP LOA RT 01/01</v>
       </c>
       <c r="G37" t="str">
         <v>LOA</v>
@@ -1810,10 +1810,10 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K37" t="str">
-        <v>Backlog 2 desil 1</v>
+        <v>Data Pengganti</v>
       </c>
       <c r="L37" t="str">
-        <v>Backlog 2 Desil 1-5</v>
+        <v>-</v>
       </c>
     </row>
     <row r="38">
@@ -1821,19 +1821,19 @@
         <v>37</v>
       </c>
       <c r="B38" t="str">
-        <v>ANAH</v>
+        <v>DANA</v>
       </c>
       <c r="C38" t="str">
-        <v>P</v>
+        <v>L</v>
       </c>
       <c r="D38" t="str">
-        <v>3204354304480004</v>
+        <v>3204352610750003</v>
       </c>
       <c r="E38" t="str">
-        <v>3204352201200003</v>
+        <v>3204351903051537</v>
       </c>
       <c r="F38" t="str">
-        <v>KP.NENGENG RT 2 RW 4</v>
+        <v>KP SUKA GEUNAH RT 01/05</v>
       </c>
       <c r="G38" t="str">
         <v>LOA</v>
@@ -1848,10 +1848,10 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K38" t="str">
-        <v>Backlog 2 desil 4</v>
+        <v>Data Pengganti</v>
       </c>
       <c r="L38" t="str">
-        <v>Backlog 2 Desil 1-5</v>
+        <v>-</v>
       </c>
     </row>
     <row r="39">
@@ -1859,19 +1859,19 @@
         <v>38</v>
       </c>
       <c r="B39" t="str">
-        <v>U.ODIN</v>
+        <v>NURHAYATI</v>
       </c>
       <c r="C39" t="str">
-        <v>L</v>
+        <v>P</v>
       </c>
       <c r="D39" t="str">
-        <v>3204351108770005</v>
+        <v>3204354805770008</v>
       </c>
       <c r="E39" t="str">
-        <v>3204351009120001</v>
+        <v>3204351903050323</v>
       </c>
       <c r="F39" t="str">
-        <v>KP.MEKARSARI RT 3 RW 9</v>
+        <v>KP CILOPANG RT 02 RW 07</v>
       </c>
       <c r="G39" t="str">
         <v>LOA</v>
@@ -1886,10 +1886,10 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K39" t="str">
-        <v>Backlog 2 desil 1</v>
+        <v>Data Pengganti</v>
       </c>
       <c r="L39" t="str">
-        <v>Backlog 2 Desil 1-5</v>
+        <v>-</v>
       </c>
     </row>
     <row r="40">
@@ -1897,19 +1897,19 @@
         <v>39</v>
       </c>
       <c r="B40" t="str">
-        <v>AAM</v>
+        <v>TARLAN</v>
       </c>
       <c r="C40" t="str">
         <v>L</v>
       </c>
       <c r="D40" t="str">
-        <v>3204350610650002</v>
+        <v>3204351808630003</v>
       </c>
       <c r="E40" t="str">
-        <v>3204352312050145</v>
+        <v>3204352405110065</v>
       </c>
       <c r="F40" t="str">
-        <v>KP.LENGO RT 2 RW 11</v>
+        <v>KP CILOPANG RT 04/07</v>
       </c>
       <c r="G40" t="str">
         <v>LOA</v>
@@ -1924,10 +1924,10 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K40" t="str">
-        <v>Backlog 2 desil 2</v>
+        <v>Data Pengganti</v>
       </c>
       <c r="L40" t="str">
-        <v>Backlog 2 Desil 1-5</v>
+        <v>-</v>
       </c>
     </row>
     <row r="41">
@@ -1935,19 +1935,19 @@
         <v>40</v>
       </c>
       <c r="B41" t="str">
-        <v>ENDANG SARGA</v>
+        <v>ICAH</v>
       </c>
       <c r="C41" t="str">
-        <v>L</v>
+        <v>P</v>
       </c>
       <c r="D41" t="str">
-        <v>3204350911550003</v>
+        <v>-</v>
       </c>
       <c r="E41" t="str">
-        <v>3204352903110009</v>
+        <v>-</v>
       </c>
       <c r="F41" t="str">
-        <v>KP.TIISDINGIN RT 2 RW 6</v>
+        <v>-</v>
       </c>
       <c r="G41" t="str">
         <v>LOA</v>
@@ -1962,10 +1962,10 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K41" t="str">
-        <v>Backlog 2 desil 2</v>
+        <v>Data Pengganti</v>
       </c>
       <c r="L41" t="str">
-        <v>Backlog 2 Desil 1-5</v>
+        <v>-</v>
       </c>
     </row>
     <row r="42">
@@ -1973,19 +1973,19 @@
         <v>41</v>
       </c>
       <c r="B42" t="str">
-        <v>ADE</v>
+        <v>ADANG</v>
       </c>
       <c r="C42" t="str">
-        <v>L</v>
+        <v>P</v>
       </c>
       <c r="D42" t="str">
-        <v>3204351205630001</v>
+        <v>3204364406880002</v>
       </c>
       <c r="E42" t="str">
-        <v>3204351903050814</v>
+        <v>3204361108120039</v>
       </c>
       <c r="F42" t="str">
-        <v>KP.MALANG RT 5 RW 6</v>
+        <v>KP CICANAR RT 1 RW 12</v>
       </c>
       <c r="G42" t="str">
         <v>LOA</v>
@@ -2000,10 +2000,10 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K42" t="str">
-        <v>Backlog 2 desil 2</v>
+        <v>-</v>
       </c>
       <c r="L42" t="str">
-        <v>Backlog 2 Desil 1-5</v>
+        <v>-</v>
       </c>
     </row>
     <row r="43">
@@ -2011,19 +2011,19 @@
         <v>42</v>
       </c>
       <c r="B43" t="str">
-        <v>TOTO TARMALA</v>
+        <v>ADE</v>
       </c>
       <c r="C43" t="str">
         <v>L</v>
       </c>
       <c r="D43" t="str">
-        <v>3204350101920031</v>
+        <v>3204351205630001</v>
       </c>
       <c r="E43" t="str">
-        <v>3204351803050561</v>
+        <v>3204351903050814</v>
       </c>
       <c r="F43" t="str">
-        <v>KP LOA RT 4 RW 2</v>
+        <v>KP MALANG RT 5 RW 6</v>
       </c>
       <c r="G43" t="str">
         <v>LOA</v>
@@ -2038,10 +2038,10 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K43" t="str">
-        <v>Tidak masuk backlog perumahan desil 1</v>
+        <v>-</v>
       </c>
       <c r="L43" t="str">
-        <v>Tidak masuk backlog perumahan</v>
+        <v>-</v>
       </c>
     </row>
     <row r="44">
@@ -2049,19 +2049,19 @@
         <v>43</v>
       </c>
       <c r="B44" t="str">
-        <v>UJANG TIMAN</v>
+        <v>ANAH</v>
       </c>
       <c r="C44" t="str">
-        <v>L</v>
+        <v>P</v>
       </c>
       <c r="D44" t="str">
-        <v>3204351508760018</v>
+        <v>3204354304480004</v>
       </c>
       <c r="E44" t="str">
-        <v>3204351211130013</v>
+        <v>3204352201200003</v>
       </c>
       <c r="F44" t="str">
-        <v>KP LOA RT 4 RW 2</v>
+        <v>KP NENGENG RT 2 RW 4</v>
       </c>
       <c r="G44" t="str">
         <v>LOA</v>
@@ -2076,10 +2076,10 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K44" t="str">
-        <v>Backlog 2 desil 2</v>
+        <v>-</v>
       </c>
       <c r="L44" t="str">
-        <v>Backlog 2 Desil 1-5</v>
+        <v>-</v>
       </c>
     </row>
     <row r="45">
@@ -2087,19 +2087,19 @@
         <v>44</v>
       </c>
       <c r="B45" t="str">
-        <v>SARIFUDIN</v>
+        <v>WAHYU WIBISANA</v>
       </c>
       <c r="C45" t="str">
         <v>L</v>
       </c>
       <c r="D45" t="str">
-        <v>3204352307940008</v>
+        <v>3204353112600001</v>
       </c>
       <c r="E45" t="str">
-        <v>3204352609140021</v>
+        <v>3204350701060146</v>
       </c>
       <c r="F45" t="str">
-        <v>KP.LOA RT 3 RW 10</v>
+        <v>LIMUS MANGGUNG RT 3 RW 8</v>
       </c>
       <c r="G45" t="str">
         <v>LOA</v>
@@ -2114,10 +2114,10 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K45" t="str">
-        <v>Backlog 2 desil 2</v>
+        <v>-</v>
       </c>
       <c r="L45" t="str">
-        <v>Backlog 2 Desil 1-5</v>
+        <v>-</v>
       </c>
     </row>
     <row r="46">
@@ -2125,19 +2125,19 @@
         <v>45</v>
       </c>
       <c r="B46" t="str">
-        <v>EMEH</v>
+        <v>ECIN</v>
       </c>
       <c r="C46" t="str">
         <v>P</v>
       </c>
       <c r="D46" t="str">
-        <v>3204354107590197</v>
+        <v>3204356010480002</v>
       </c>
       <c r="E46" t="str">
-        <v>3204352210070031</v>
+        <v>3204352312050057</v>
       </c>
       <c r="F46" t="str">
-        <v>MALINGPING RT 4 RW 8</v>
+        <v>KP BARUNAI RT 00/04</v>
       </c>
       <c r="G46" t="str">
         <v>LOA</v>
@@ -2152,10 +2152,10 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K46" t="str">
-        <v>Tidak masuk backlog perumahan desil 2</v>
+        <v>Data Pengganti</v>
       </c>
       <c r="L46" t="str">
-        <v>Tidak masuk backlog perumahan</v>
+        <v>-</v>
       </c>
     </row>
     <row r="47">
@@ -2163,19 +2163,19 @@
         <v>46</v>
       </c>
       <c r="B47" t="str">
-        <v>TATAN RUSTANDI</v>
+        <v>EKUR</v>
       </c>
       <c r="C47" t="str">
         <v>L</v>
       </c>
       <c r="D47" t="str">
-        <v>3203151003900004</v>
+        <v>-</v>
       </c>
       <c r="E47" t="str">
-        <v>3204350304200001</v>
+        <v>-</v>
       </c>
       <c r="F47" t="str">
-        <v>KP LOA RT 4 RW 2</v>
+        <v>-</v>
       </c>
       <c r="G47" t="str">
         <v>LOA</v>
@@ -2190,10 +2190,10 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K47" t="str">
-        <v>Backlog 2 desil 2</v>
+        <v>Data Pengganti</v>
       </c>
       <c r="L47" t="str">
-        <v>Backlog 2 Desil 1-5</v>
+        <v>-</v>
       </c>
     </row>
     <row r="48">
@@ -2201,19 +2201,19 @@
         <v>47</v>
       </c>
       <c r="B48" t="str">
-        <v>HADI</v>
+        <v>CARMA</v>
       </c>
       <c r="C48" t="str">
         <v>L</v>
       </c>
       <c r="D48" t="str">
-        <v>3204352502820008</v>
+        <v>-</v>
       </c>
       <c r="E48" t="str">
-        <v>3204351004070008</v>
+        <v>-</v>
       </c>
       <c r="F48" t="str">
-        <v>CIDADAP RT 5 RW 5</v>
+        <v>-</v>
       </c>
       <c r="G48" t="str">
         <v>LOA</v>
@@ -2228,10 +2228,10 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K48" t="str">
-        <v>Backlog 2 desil 3</v>
+        <v>Data Pengganti</v>
       </c>
       <c r="L48" t="str">
-        <v>Backlog 2 Desil 1-5</v>
+        <v>-</v>
       </c>
     </row>
     <row r="49">
@@ -2239,19 +2239,19 @@
         <v>48</v>
       </c>
       <c r="B49" t="str">
-        <v>WAHYU WIBISANA</v>
+        <v>UJANG JUJUN</v>
       </c>
       <c r="C49" t="str">
         <v>L</v>
       </c>
       <c r="D49" t="str">
-        <v>3204353112600001</v>
+        <v>-</v>
       </c>
       <c r="E49" t="str">
-        <v>3204350701060146</v>
+        <v>-</v>
       </c>
       <c r="F49" t="str">
-        <v>LIMUS MANGGUNG   RT 3 RW 8</v>
+        <v>-</v>
       </c>
       <c r="G49" t="str">
         <v>LOA</v>
@@ -2266,10 +2266,10 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K49" t="str">
-        <v>Backlog 2 desil 3</v>
+        <v>Data Pengganti</v>
       </c>
       <c r="L49" t="str">
-        <v>Backlog 2 Desil 1-5</v>
+        <v>-</v>
       </c>
     </row>
     <row r="50">
@@ -2277,19 +2277,19 @@
         <v>49</v>
       </c>
       <c r="B50" t="str">
-        <v>ILPAN SETIA MULYA</v>
+        <v>UJANG PARMAN</v>
       </c>
       <c r="C50" t="str">
         <v>L</v>
       </c>
       <c r="D50" t="str">
-        <v>3204332811900005</v>
+        <v>-</v>
       </c>
       <c r="E50" t="str">
-        <v>3204352506130041</v>
+        <v>-</v>
       </c>
       <c r="F50" t="str">
-        <v>KP. TIISDINGIN RT 1 RW 6</v>
+        <v>-</v>
       </c>
       <c r="G50" t="str">
         <v>LOA</v>
@@ -2304,281 +2304,15 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K50" t="str">
-        <v>Backlog 2 desil 2</v>
+        <v>Data Baru</v>
       </c>
       <c r="L50" t="str">
-        <v>Backlog 2 Desil 1-5</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>SAEPULOH</v>
-      </c>
-      <c r="C51" t="str">
-        <v>L</v>
-      </c>
-      <c r="D51" t="str">
-        <v>3204351406940003</v>
-      </c>
-      <c r="E51" t="str">
-        <v>3204352909220007</v>
-      </c>
-      <c r="F51" t="str">
-        <v>KP. LOA RT 3 RW 10</v>
-      </c>
-      <c r="G51" t="str">
-        <v>LOA</v>
-      </c>
-      <c r="H51" t="str">
-        <v>PASEH</v>
-      </c>
-      <c r="I51" t="str">
-        <v>KAB. BANDUNG</v>
-      </c>
-      <c r="J51" t="str">
-        <v>JAWA BARAT</v>
-      </c>
-      <c r="K51" t="str">
-        <v>Backlog 2 desil 4</v>
-      </c>
-      <c r="L51" t="str">
-        <v>Backlog 2 Desil 1-5</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>NURHAYATI</v>
-      </c>
-      <c r="C52" t="str">
-        <v>P</v>
-      </c>
-      <c r="D52" t="str">
-        <v>3204354805770008</v>
-      </c>
-      <c r="E52" t="str">
-        <v>3204351903050323</v>
-      </c>
-      <c r="F52" t="str">
-        <v>KP CILOPANG RT 02 RW 07</v>
-      </c>
-      <c r="G52" t="str">
-        <v>LOA</v>
-      </c>
-      <c r="H52" t="str">
-        <v>PASEH</v>
-      </c>
-      <c r="I52" t="str">
-        <v>KAB. BANDUNG</v>
-      </c>
-      <c r="J52" t="str">
-        <v>JAWA BARAT</v>
-      </c>
-      <c r="K52" t="str">
-        <v>Data Pengganti</v>
-      </c>
-      <c r="L52" t="str">
-        <v>-</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>ECIN</v>
-      </c>
-      <c r="C53" t="str">
-        <v>P</v>
-      </c>
-      <c r="D53" t="str">
-        <v>3204356010480002</v>
-      </c>
-      <c r="E53" t="str">
-        <v>3204352312050057</v>
-      </c>
-      <c r="F53" t="str">
-        <v>KP BARUNAI RT 00/04</v>
-      </c>
-      <c r="G53" t="str">
-        <v>LOA</v>
-      </c>
-      <c r="H53" t="str">
-        <v>PASEH</v>
-      </c>
-      <c r="I53" t="str">
-        <v>KAB. BANDUNG</v>
-      </c>
-      <c r="J53" t="str">
-        <v>JAWA BARAT</v>
-      </c>
-      <c r="K53" t="str">
-        <v>Data Pengganti</v>
-      </c>
-      <c r="L53" t="str">
-        <v>-</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>ASEP AAN SAEPUDIN</v>
-      </c>
-      <c r="C54" t="str">
-        <v>L</v>
-      </c>
-      <c r="D54" t="str">
-        <v>3204350901750002</v>
-      </c>
-      <c r="E54" t="str">
-        <v>3204351208160008</v>
-      </c>
-      <c r="F54" t="str">
-        <v>KP LOA RT 01/01</v>
-      </c>
-      <c r="G54" t="str">
-        <v>LOA</v>
-      </c>
-      <c r="H54" t="str">
-        <v>PASEH</v>
-      </c>
-      <c r="I54" t="str">
-        <v>KAB. BANDUNG</v>
-      </c>
-      <c r="J54" t="str">
-        <v>JAWA BARAT</v>
-      </c>
-      <c r="K54" t="str">
-        <v>Data Pengganti</v>
-      </c>
-      <c r="L54" t="str">
-        <v>-</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>DANA</v>
-      </c>
-      <c r="C55" t="str">
-        <v>L</v>
-      </c>
-      <c r="D55" t="str">
-        <v>3204352610750003</v>
-      </c>
-      <c r="E55" t="str">
-        <v>3204351903051537</v>
-      </c>
-      <c r="F55" t="str">
-        <v>KP SUKA GEUNAH RT 01/05</v>
-      </c>
-      <c r="G55" t="str">
-        <v>LOA</v>
-      </c>
-      <c r="H55" t="str">
-        <v>PASEH</v>
-      </c>
-      <c r="I55" t="str">
-        <v>KAB. BANDUNG</v>
-      </c>
-      <c r="J55" t="str">
-        <v>JAWA BARAT</v>
-      </c>
-      <c r="K55" t="str">
-        <v>Data Pengganti</v>
-      </c>
-      <c r="L55" t="str">
-        <v>-</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>TARLAN</v>
-      </c>
-      <c r="C56" t="str">
-        <v>L</v>
-      </c>
-      <c r="D56" t="str">
-        <v>3204351808630003</v>
-      </c>
-      <c r="E56" t="str">
-        <v>3204352405110065</v>
-      </c>
-      <c r="F56" t="str">
-        <v>KP CILOPANG RT 04/07</v>
-      </c>
-      <c r="G56" t="str">
-        <v>LOA</v>
-      </c>
-      <c r="H56" t="str">
-        <v>PASEH</v>
-      </c>
-      <c r="I56" t="str">
-        <v>KAB. BANDUNG</v>
-      </c>
-      <c r="J56" t="str">
-        <v>JAWA BARAT</v>
-      </c>
-      <c r="K56" t="str">
-        <v>Data Pengganti</v>
-      </c>
-      <c r="L56" t="str">
-        <v>-</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>AHMAD</v>
-      </c>
-      <c r="C57" t="str">
-        <v>L</v>
-      </c>
-      <c r="D57" t="str">
-        <v>3204351702540001</v>
-      </c>
-      <c r="E57" t="str">
-        <v>3204352508050248</v>
-      </c>
-      <c r="F57" t="str">
-        <v>KP. CILOPANG 001/003</v>
-      </c>
-      <c r="G57" t="str">
-        <v>LOA</v>
-      </c>
-      <c r="H57" t="str">
-        <v>PASEH</v>
-      </c>
-      <c r="I57" t="str">
-        <v>KAB. BANDUNG</v>
-      </c>
-      <c r="J57" t="str">
-        <v>JAWA BARAT</v>
-      </c>
-      <c r="K57" t="str">
-        <v>Data Pengganti</v>
-      </c>
-      <c r="L57" t="str">
         <v>-</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L57"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L50"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2632,7 +2366,7 @@
         <v>Total Penerima</v>
       </c>
       <c r="B6" t="str">
-        <v>56 orang</v>
+        <v>49 orang</v>
       </c>
     </row>
     <row r="7">
@@ -2656,7 +2390,7 @@
         <v>LOA (PASEH)</v>
       </c>
       <c r="B9" t="str">
-        <v>20 + 6 pengganti orang</v>
+        <v>19 orang</v>
       </c>
     </row>
     <row r="10">
@@ -2664,7 +2398,7 @@
         <v>Laki-laki</v>
       </c>
       <c r="B10" t="str">
-        <v>43 orang</v>
+        <v>51 orang</v>
       </c>
     </row>
     <row r="11">
@@ -2672,7 +2406,7 @@
         <v>Perempuan</v>
       </c>
       <c r="B11" t="str">
-        <v>13 orang</v>
+        <v>18 orang</v>
       </c>
     </row>
   </sheetData>

--- a/upload/Data_Riska_Ujang_TFL_IBUN.xlsx
+++ b/upload/Data_Riska_Ujang_TFL_IBUN.xlsx
@@ -5,6 +5,7 @@
   <sheets>
     <sheet name="Data Penerima" sheetId="1" r:id="rId1"/>
     <sheet name="Ringkasan" sheetId="2" r:id="rId2"/>
+    <sheet name="Tidak ACC - LOA" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -472,7 +473,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K2" t="str">
-        <v>Backlog 2 desil 2</v>
+        <v>ACC</v>
       </c>
       <c r="L2" t="str">
         <v>Backlog 2 Desil 1-5</v>
@@ -511,7 +512,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K3" t="str">
-        <v>Tidak masuk backlog perumahan desil 4</v>
+        <v>ACC</v>
       </c>
       <c r="L3" t="str">
         <v>Tidak masuk backlog perumahan</v>
@@ -550,7 +551,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K4" t="str">
-        <v>Backlog 2 desil 4</v>
+        <v>ACC</v>
       </c>
       <c r="L4" t="str">
         <v>Backlog 2 Desil 1-5</v>
@@ -589,7 +590,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K5" t="str">
-        <v>Backlog 1 desil 4</v>
+        <v>ACC</v>
       </c>
       <c r="L5" t="str">
         <v>Backlog 1 Desil 1-5</v>
@@ -628,7 +629,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K6" t="str">
-        <v>Backlog 2 desil 3</v>
+        <v>ACC</v>
       </c>
       <c r="L6" t="str">
         <v>Backlog 2 Desil 1-5</v>
@@ -667,7 +668,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K7" t="str">
-        <v>Backlog 2 desil 2</v>
+        <v>ACC</v>
       </c>
       <c r="L7" t="str">
         <v>Backlog 2 Desil 1-5</v>
@@ -706,7 +707,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K8" t="str">
-        <v>Backlog 1 desil 1</v>
+        <v>ACC</v>
       </c>
       <c r="L8" t="str">
         <v>Backlog 1 Desil 1-5</v>
@@ -745,7 +746,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K9" t="str">
-        <v>Backlog 2 desil 1</v>
+        <v>ACC</v>
       </c>
       <c r="L9" t="str">
         <v>Backlog 2 Desil 1-5</v>
@@ -784,7 +785,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K10" t="str">
-        <v>Backlog 2 desil 2</v>
+        <v>ACC</v>
       </c>
       <c r="L10" t="str">
         <v>Backlog 2 Desil 1-5</v>
@@ -822,7 +823,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K11" t="str">
-        <v>Tidak masuk backlog perumahan desil 1</v>
+        <v>ACC</v>
       </c>
       <c r="L11" t="str">
         <v>Tidak masuk backlog perumahan</v>
@@ -860,7 +861,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K12" t="str">
-        <v>Backlog 2 desil 6</v>
+        <v>ACC</v>
       </c>
       <c r="L12" t="str">
         <v>Backlog 2 Desil 6-10</v>
@@ -898,7 +899,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K13" t="str">
-        <v>Backlog 2 desil 4</v>
+        <v>ACC</v>
       </c>
       <c r="L13" t="str">
         <v>Backlog 2 Desil 1-5</v>
@@ -936,7 +937,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K14" t="str">
-        <v>Tidak masuk backlog perumahan desil 6</v>
+        <v>ACC</v>
       </c>
       <c r="L14" t="str">
         <v>Tidak masuk backlog perumahan</v>
@@ -974,7 +975,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K15" t="str">
-        <v>Tidak masuk backlog perumahan desil 1</v>
+        <v>ACC</v>
       </c>
       <c r="L15" t="str">
         <v>Tidak masuk backlog perumahan</v>
@@ -1012,7 +1013,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K16" t="str">
-        <v>Backlog 2 desil 5</v>
+        <v>ACC</v>
       </c>
       <c r="L16" t="str">
         <v>Backlog 2 Desil 1-5</v>
@@ -1050,7 +1051,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K17" t="str">
-        <v>Backlog 2 desil 6 | Data Pengganti</v>
+        <v>ACC - Data Pengganti</v>
       </c>
       <c r="L17" t="str">
         <v>Backlog 2 Desil 6-10</v>
@@ -1088,7 +1089,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K18" t="str">
-        <v>Backlog 2 desil 1 | Data Pengganti</v>
+        <v>ACC - Data Pengganti</v>
       </c>
       <c r="L18" t="str">
         <v>Backlog 2 Desil 1-5</v>
@@ -1126,7 +1127,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K19" t="str">
-        <v>Backlog 2 desil 2 | Data Pengganti</v>
+        <v>ACC - Data Pengganti</v>
       </c>
       <c r="L19" t="str">
         <v>Backlog 2 Desil 1-5</v>
@@ -1164,7 +1165,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K20" t="str">
-        <v>Backlog 2 desil 2 | Data Pengganti</v>
+        <v>ACC - Data Pengganti</v>
       </c>
       <c r="L20" t="str">
         <v>Backlog 2 Desil 1-5</v>
@@ -1202,7 +1203,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K21" t="str">
-        <v>Backlog 2 desil 2 | Data Pengganti</v>
+        <v>ACC - Data Pengganti</v>
       </c>
       <c r="L21" t="str">
         <v>Backlog 2 Desil 1-5</v>
@@ -1240,7 +1241,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K22" t="str">
-        <v>Backlog 2 desil 1</v>
+        <v>ACC</v>
       </c>
       <c r="L22" t="str">
         <v>Backlog 2 Desil 1-5</v>
@@ -1278,7 +1279,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K23" t="str">
-        <v>Backlog 2 desil 1</v>
+        <v>ACC</v>
       </c>
       <c r="L23" t="str">
         <v>Backlog 2 Desil 1-5</v>
@@ -1316,7 +1317,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K24" t="str">
-        <v>Backlog 2 desil 3</v>
+        <v>ACC</v>
       </c>
       <c r="L24" t="str">
         <v>Backlog 2 Desil 1-5</v>
@@ -1354,7 +1355,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K25" t="str">
-        <v>Backlog 1 desil 4</v>
+        <v>ACC</v>
       </c>
       <c r="L25" t="str">
         <v>Backlog 1 Desil 1-5</v>
@@ -1392,7 +1393,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K26" t="str">
-        <v>Backlog 2 desil 2 | Data Pengganti</v>
+        <v>ACC - Data Pengganti</v>
       </c>
       <c r="L26" t="str">
         <v>Backlog 2 Desil 1-5</v>
@@ -1430,7 +1431,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K27" t="str">
-        <v>Backlog 2 desil 5</v>
+        <v>ACC</v>
       </c>
       <c r="L27" t="str">
         <v>Backlog 2 Desil 1-5</v>
@@ -1468,7 +1469,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K28" t="str">
-        <v>Tidak masuk backlog perumahan desil 3</v>
+        <v>ACC</v>
       </c>
       <c r="L28" t="str">
         <v>Tidak masuk backlog perumahan</v>
@@ -1506,7 +1507,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K29" t="str">
-        <v>Backlog 2 desil 2</v>
+        <v>ACC</v>
       </c>
       <c r="L29" t="str">
         <v>Backlog 2 Desil 1-5</v>
@@ -1544,7 +1545,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K30" t="str">
-        <v/>
+        <v>ACC</v>
       </c>
       <c r="L30" t="str">
         <v>-</v>
@@ -1582,7 +1583,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K31" t="str">
-        <v>Backlog 2 desil 3</v>
+        <v>ACC</v>
       </c>
       <c r="L31" t="str">
         <v>Backlog 2 Desil 1-5</v>
@@ -1620,7 +1621,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K32" t="str">
-        <v>-</v>
+        <v>ACC</v>
       </c>
       <c r="L32" t="str">
         <v>-</v>
@@ -1658,7 +1659,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K33" t="str">
-        <v>-</v>
+        <v>ACC</v>
       </c>
       <c r="L33" t="str">
         <v>-</v>
@@ -1696,7 +1697,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K34" t="str">
-        <v>-</v>
+        <v>ACC</v>
       </c>
       <c r="L34" t="str">
         <v>-</v>
@@ -1734,7 +1735,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K35" t="str">
-        <v>-</v>
+        <v>ACC</v>
       </c>
       <c r="L35" t="str">
         <v>-</v>
@@ -1772,7 +1773,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K36" t="str">
-        <v>Data Baru</v>
+        <v>ACC - Data Baru</v>
       </c>
       <c r="L36" t="str">
         <v>-</v>
@@ -1810,7 +1811,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K37" t="str">
-        <v>Data Pengganti</v>
+        <v>ACC</v>
       </c>
       <c r="L37" t="str">
         <v>-</v>
@@ -1848,7 +1849,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K38" t="str">
-        <v>Data Pengganti</v>
+        <v>ACC</v>
       </c>
       <c r="L38" t="str">
         <v>-</v>
@@ -1886,7 +1887,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K39" t="str">
-        <v>Data Pengganti</v>
+        <v>ACC</v>
       </c>
       <c r="L39" t="str">
         <v>-</v>
@@ -1924,7 +1925,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K40" t="str">
-        <v>Data Pengganti</v>
+        <v>ACC</v>
       </c>
       <c r="L40" t="str">
         <v>-</v>
@@ -1962,7 +1963,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K41" t="str">
-        <v>Data Pengganti</v>
+        <v>ACC</v>
       </c>
       <c r="L41" t="str">
         <v>-</v>
@@ -2000,7 +2001,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K42" t="str">
-        <v>-</v>
+        <v>ACC</v>
       </c>
       <c r="L42" t="str">
         <v>-</v>
@@ -2038,7 +2039,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K43" t="str">
-        <v>-</v>
+        <v>ACC</v>
       </c>
       <c r="L43" t="str">
         <v>-</v>
@@ -2076,7 +2077,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K44" t="str">
-        <v>-</v>
+        <v>ACC</v>
       </c>
       <c r="L44" t="str">
         <v>-</v>
@@ -2114,7 +2115,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K45" t="str">
-        <v>-</v>
+        <v>ACC</v>
       </c>
       <c r="L45" t="str">
         <v>-</v>
@@ -2152,7 +2153,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K46" t="str">
-        <v>Data Pengganti</v>
+        <v>ACC</v>
       </c>
       <c r="L46" t="str">
         <v>-</v>
@@ -2190,7 +2191,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K47" t="str">
-        <v>Data Pengganti</v>
+        <v>ACC</v>
       </c>
       <c r="L47" t="str">
         <v>-</v>
@@ -2228,7 +2229,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K48" t="str">
-        <v>Data Pengganti</v>
+        <v>ACC</v>
       </c>
       <c r="L48" t="str">
         <v>-</v>
@@ -2266,7 +2267,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K49" t="str">
-        <v>Data Pengganti</v>
+        <v>ACC</v>
       </c>
       <c r="L49" t="str">
         <v>-</v>
@@ -2304,7 +2305,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K50" t="str">
-        <v>Data Baru</v>
+        <v>ACC - Data Baru</v>
       </c>
       <c r="L50" t="str">
         <v>-</v>
@@ -2319,7 +2320,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2398,7 +2399,7 @@
         <v>Laki-laki</v>
       </c>
       <c r="B10" t="str">
-        <v>51 orang</v>
+        <v>37 orang</v>
       </c>
     </row>
     <row r="11">
@@ -2406,12 +2407,355 @@
         <v>Perempuan</v>
       </c>
       <c r="B11" t="str">
-        <v>18 orang</v>
+        <v>12 orang</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>LOA - Tidak ACC</v>
+      </c>
+      <c r="B12" t="str">
+        <v>12 orang</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>LOA - ACC</v>
+      </c>
+      <c r="B13" t="str">
+        <v>19 orang</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Alasan Tidak ACC</v>
+      </c>
+      <c r="B14" t="str">
+        <v>11 Layak Huni, 1 Tidak Melanjutkan</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B14"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G13"/>
+  <cols>
+    <col min="1" max="1" width="5.83203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
+    <col min="3" max="3" width="5.83203125" customWidth="1"/>
+    <col min="4" max="4" width="20.83203125" customWidth="1"/>
+    <col min="5" max="5" width="22.83203125" customWidth="1"/>
+    <col min="6" max="6" width="28.83203125" customWidth="1"/>
+    <col min="7" max="7" width="28.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>NO</v>
+      </c>
+      <c r="B1" t="str">
+        <v>NAMA</v>
+      </c>
+      <c r="C1" t="str">
+        <v>L/P</v>
+      </c>
+      <c r="D1" t="str">
+        <v>NO KTP</v>
+      </c>
+      <c r="E1" t="str">
+        <v>NO KK</v>
+      </c>
+      <c r="F1" t="str">
+        <v>ALAMAT</v>
+      </c>
+      <c r="G1" t="str">
+        <v>ALASAN TIDAK ACC</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>EHA</v>
+      </c>
+      <c r="C2" t="str">
+        <v>P</v>
+      </c>
+      <c r="D2" t="str">
+        <v>3204355002550004</v>
+      </c>
+      <c r="E2" t="str">
+        <v>3204353009220015</v>
+      </c>
+      <c r="F2" t="str">
+        <v>KP. LOA RT 3 RW 10</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Layak Huni</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>LALAN</v>
+      </c>
+      <c r="C3" t="str">
+        <v>L</v>
+      </c>
+      <c r="D3" t="str">
+        <v>3204352905980001</v>
+      </c>
+      <c r="E3" t="str">
+        <v>3204351612210006</v>
+      </c>
+      <c r="F3" t="str">
+        <v>KP. CIDADAP RT 5 RW 5</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Layak Huni</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>WARSA</v>
+      </c>
+      <c r="C4" t="str">
+        <v>L</v>
+      </c>
+      <c r="D4" t="str">
+        <v>3204351002711001</v>
+      </c>
+      <c r="E4" t="str">
+        <v>3204351609140013</v>
+      </c>
+      <c r="F4" t="str">
+        <v>KP. BUKATANAH RT 2 RW 3</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Tidak ingin melanjutkan</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>U.ODIN</v>
+      </c>
+      <c r="C5" t="str">
+        <v>L</v>
+      </c>
+      <c r="D5" t="str">
+        <v>3204351108770005</v>
+      </c>
+      <c r="E5" t="str">
+        <v>3204351009120001</v>
+      </c>
+      <c r="F5" t="str">
+        <v>KP. MEKARSARI RT 3 RW 9</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Layak Huni</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>ENDANG SARGA</v>
+      </c>
+      <c r="C6" t="str">
+        <v>L</v>
+      </c>
+      <c r="D6" t="str">
+        <v>3204350911550003</v>
+      </c>
+      <c r="E6" t="str">
+        <v>3204352903110009</v>
+      </c>
+      <c r="F6" t="str">
+        <v>KP. TIISDINGIN RT 2 RW 6</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Layak Huni</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>TOTO TARMALA</v>
+      </c>
+      <c r="C7" t="str">
+        <v>L</v>
+      </c>
+      <c r="D7" t="str">
+        <v>3204350101920031</v>
+      </c>
+      <c r="E7" t="str">
+        <v>3204351803050561</v>
+      </c>
+      <c r="F7" t="str">
+        <v>KP LOA RT 4 RW 2</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Layak Huni</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>UJANG TIMAN</v>
+      </c>
+      <c r="C8" t="str">
+        <v>L</v>
+      </c>
+      <c r="D8" t="str">
+        <v>3204351508760018</v>
+      </c>
+      <c r="E8" t="str">
+        <v>3204351211130013</v>
+      </c>
+      <c r="F8" t="str">
+        <v>KP LOA RT 4 RW 2</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Layak Huni</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>EMEH</v>
+      </c>
+      <c r="C9" t="str">
+        <v>P</v>
+      </c>
+      <c r="D9" t="str">
+        <v>3204354107590197</v>
+      </c>
+      <c r="E9" t="str">
+        <v>3204352210070031</v>
+      </c>
+      <c r="F9" t="str">
+        <v>MALINGPING RT 4 RW 8</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Layak Huni</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>TATAN RUSTANDI</v>
+      </c>
+      <c r="C10" t="str">
+        <v>L</v>
+      </c>
+      <c r="D10" t="str">
+        <v>3203151003900004</v>
+      </c>
+      <c r="E10" t="str">
+        <v>3204350304200001</v>
+      </c>
+      <c r="F10" t="str">
+        <v>KP LOA RT 4 RW 2</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Layak Huni</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>HADI</v>
+      </c>
+      <c r="C11" t="str">
+        <v>L</v>
+      </c>
+      <c r="D11" t="str">
+        <v>3204352502820008</v>
+      </c>
+      <c r="E11" t="str">
+        <v>3204351004070008</v>
+      </c>
+      <c r="F11" t="str">
+        <v>CIDADAP RT 5 RW 5</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Layak Huni</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>ILPAN SETIA MULYA</v>
+      </c>
+      <c r="C12" t="str">
+        <v>L</v>
+      </c>
+      <c r="D12" t="str">
+        <v>3204332811900005</v>
+      </c>
+      <c r="E12" t="str">
+        <v>3204352506130041</v>
+      </c>
+      <c r="F12" t="str">
+        <v>KP. TIISDINGIN RT 1 RW 6</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Layak Huni</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>SAEPULOH</v>
+      </c>
+      <c r="C13" t="str">
+        <v>L</v>
+      </c>
+      <c r="D13" t="str">
+        <v>3204351406940003</v>
+      </c>
+      <c r="E13" t="str">
+        <v>3204352909220007</v>
+      </c>
+      <c r="F13" t="str">
+        <v>KP. LOA RT 3 RW 10</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Layak Huni</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/upload/Data_Riska_Ujang_TFL_IBUN.xlsx
+++ b/upload/Data_Riska_Ujang_TFL_IBUN.xlsx
@@ -1621,7 +1621,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K32" t="str">
-        <v>ACC</v>
+        <v>ACC - Backlog 2 desil 5</v>
       </c>
       <c r="L32" t="str">
         <v>-</v>
@@ -1659,7 +1659,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K33" t="str">
-        <v>ACC</v>
+        <v>ACC - Backlog 2 desil 2</v>
       </c>
       <c r="L33" t="str">
         <v>-</v>
@@ -1697,7 +1697,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K34" t="str">
-        <v>ACC</v>
+        <v>ACC - Backlog 2 desil 1</v>
       </c>
       <c r="L34" t="str">
         <v>-</v>
@@ -1735,7 +1735,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K35" t="str">
-        <v>ACC</v>
+        <v>ACC - Backlog 2 desil 3</v>
       </c>
       <c r="L35" t="str">
         <v>-</v>
@@ -1811,7 +1811,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K37" t="str">
-        <v>ACC</v>
+        <v>ACC - Data Pengganti</v>
       </c>
       <c r="L37" t="str">
         <v>-</v>
@@ -1849,7 +1849,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K38" t="str">
-        <v>ACC</v>
+        <v>ACC - Data Pengganti</v>
       </c>
       <c r="L38" t="str">
         <v>-</v>
@@ -1887,7 +1887,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K39" t="str">
-        <v>ACC</v>
+        <v>ACC - Data Pengganti</v>
       </c>
       <c r="L39" t="str">
         <v>-</v>
@@ -1925,7 +1925,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K40" t="str">
-        <v>ACC</v>
+        <v>ACC - Data Pengganti</v>
       </c>
       <c r="L40" t="str">
         <v>-</v>
@@ -1942,13 +1942,13 @@
         <v>P</v>
       </c>
       <c r="D41" t="str">
-        <v>-</v>
+        <v>3204354107710061</v>
       </c>
       <c r="E41" t="str">
-        <v>-</v>
+        <v>3204352304200006</v>
       </c>
       <c r="F41" t="str">
-        <v>-</v>
+        <v>Sempak RT 003 RW 005</v>
       </c>
       <c r="G41" t="str">
         <v>LOA</v>
@@ -1963,7 +1963,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K41" t="str">
-        <v>ACC</v>
+        <v>ACC - Data Pengganti</v>
       </c>
       <c r="L41" t="str">
         <v>-</v>
@@ -2001,7 +2001,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K42" t="str">
-        <v>ACC</v>
+        <v>ACC - Backlog 2 desil 1</v>
       </c>
       <c r="L42" t="str">
         <v>-</v>
@@ -2039,7 +2039,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K43" t="str">
-        <v>ACC</v>
+        <v>ACC - Backlog 2 desil 1</v>
       </c>
       <c r="L43" t="str">
         <v>-</v>
@@ -2077,7 +2077,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K44" t="str">
-        <v>ACC</v>
+        <v>ACC - Backlog 2 desil 2</v>
       </c>
       <c r="L44" t="str">
         <v>-</v>
@@ -2115,7 +2115,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K45" t="str">
-        <v>ACC</v>
+        <v>ACC - Backlog 2 desil 2</v>
       </c>
       <c r="L45" t="str">
         <v>-</v>
@@ -2153,7 +2153,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K46" t="str">
-        <v>ACC</v>
+        <v>ACC - Data Pengganti</v>
       </c>
       <c r="L46" t="str">
         <v>-</v>
@@ -2170,13 +2170,13 @@
         <v>L</v>
       </c>
       <c r="D47" t="str">
-        <v>-</v>
+        <v>3204354903820003</v>
       </c>
       <c r="E47" t="str">
-        <v>-</v>
+        <v>3204351210230005</v>
       </c>
       <c r="F47" t="str">
-        <v>-</v>
+        <v>KP LOA RT 003 RW 010</v>
       </c>
       <c r="G47" t="str">
         <v>LOA</v>
@@ -2191,7 +2191,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K47" t="str">
-        <v>ACC</v>
+        <v>ACC - Data Pengganti</v>
       </c>
       <c r="L47" t="str">
         <v>-</v>
@@ -2202,19 +2202,19 @@
         <v>47</v>
       </c>
       <c r="B48" t="str">
-        <v>CARMA</v>
+        <v>CARMA DEDI</v>
       </c>
       <c r="C48" t="str">
         <v>L</v>
       </c>
       <c r="D48" t="str">
-        <v>-</v>
+        <v>3204351207600004</v>
       </c>
       <c r="E48" t="str">
-        <v>-</v>
+        <v>3204350101060016</v>
       </c>
       <c r="F48" t="str">
-        <v>-</v>
+        <v>KP CIDADAP RT 004 RW 005</v>
       </c>
       <c r="G48" t="str">
         <v>LOA</v>
@@ -2229,7 +2229,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K48" t="str">
-        <v>ACC</v>
+        <v>ACC - Data Pengganti</v>
       </c>
       <c r="L48" t="str">
         <v>-</v>
@@ -2246,13 +2246,13 @@
         <v>L</v>
       </c>
       <c r="D49" t="str">
-        <v>-</v>
+        <v>3204350204580001</v>
       </c>
       <c r="E49" t="str">
-        <v>-</v>
+        <v>3204351803050591</v>
       </c>
       <c r="F49" t="str">
-        <v>-</v>
+        <v>KP LOA RT 003 RW 002</v>
       </c>
       <c r="G49" t="str">
         <v>LOA</v>
@@ -2267,7 +2267,7 @@
         <v>JAWA BARAT</v>
       </c>
       <c r="K49" t="str">
-        <v>ACC</v>
+        <v>ACC - Data Pengganti</v>
       </c>
       <c r="L49" t="str">
         <v>-</v>
@@ -2284,13 +2284,13 @@
         <v>L</v>
       </c>
       <c r="D50" t="str">
-        <v>-</v>
+        <v>3204351205570001</v>
       </c>
       <c r="E50" t="str">
-        <v>-</v>
+        <v>3204351803051054</v>
       </c>
       <c r="F50" t="str">
-        <v>-</v>
+        <v>KP LENGO RT 004 RW 001</v>
       </c>
       <c r="G50" t="str">
         <v>LOA</v>
@@ -2444,15 +2444,6 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G13"/>
-  <cols>
-    <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="22.83203125" customWidth="1"/>
-    <col min="3" max="3" width="5.83203125" customWidth="1"/>
-    <col min="4" max="4" width="20.83203125" customWidth="1"/>
-    <col min="5" max="5" width="22.83203125" customWidth="1"/>
-    <col min="6" max="6" width="28.83203125" customWidth="1"/>
-    <col min="7" max="7" width="28.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
